--- a/jira_export_2026-08-14.xlsx
+++ b/jira_export_2026-08-14.xlsx
@@ -815,7 +815,7 @@
     <row r="16" ht="26" customHeight="1">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>173 h</t>
+          <t>176 h</t>
         </is>
       </c>
       <c r="B16" s="7" t="n"/>
@@ -829,7 +829,7 @@
       <c r="F16" s="7" t="n"/>
       <c r="G16" s="8" t="inlineStr">
         <is>
-          <t>44.8%</t>
+          <t>45.4%</t>
         </is>
       </c>
       <c r="H16" s="7" t="n"/>
@@ -933,7 +933,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P115"/>
+  <dimension ref="A1:P116"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="43" customWidth="1" min="1" max="1"/>
@@ -942,7 +942,7 @@
     <col width="50" customWidth="1" min="4" max="4"/>
     <col width="50" customWidth="1" min="5" max="5"/>
     <col width="13" customWidth="1" min="6" max="6"/>
-    <col width="21" customWidth="1" min="7" max="7"/>
+    <col width="27" customWidth="1" min="7" max="7"/>
     <col width="22" customWidth="1" min="8" max="8"/>
     <col width="16" customWidth="1" min="9" max="9"/>
     <col width="20" customWidth="1" min="10" max="10"/>
@@ -1741,7 +1741,7 @@
         <v>1</v>
       </c>
       <c r="K14" s="14" t="n">
-        <v>0.25</v>
+        <v>0.75</v>
       </c>
       <c r="L14" s="14" t="inlineStr">
         <is>
@@ -7789,7 +7789,7 @@
         <v>16</v>
       </c>
       <c r="K99" s="11" t="n">
-        <v>5.25</v>
+        <v>5.75</v>
       </c>
       <c r="L99" s="11" t="inlineStr">
         <is>
@@ -8057,7 +8057,7 @@
         <v>20</v>
       </c>
       <c r="K103" s="11" t="n">
-        <v>1.25</v>
+        <v>1.75</v>
       </c>
       <c r="L103" s="11" t="inlineStr"/>
       <c r="M103" s="11" t="inlineStr"/>
@@ -8719,7 +8719,7 @@
         <v>35</v>
       </c>
       <c r="K113" s="11" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="L113" s="11" t="inlineStr"/>
       <c r="M113" s="11" t="inlineStr"/>
@@ -8794,31 +8794,83 @@
       </c>
     </row>
     <row r="115">
-      <c r="A115" s="17" t="inlineStr">
+      <c r="A115" s="10" t="inlineStr">
+        <is>
+          <t>PSC-1326</t>
+        </is>
+      </c>
+      <c r="B115" s="11" t="inlineStr">
+        <is>
+          <t>MAIRIE DE SAINT-ISMIER</t>
+        </is>
+      </c>
+      <c r="C115" s="11" t="inlineStr"/>
+      <c r="D115" s="11" t="inlineStr">
+        <is>
+          <t>MAIRIE DE SAINT-ISMIER</t>
+        </is>
+      </c>
+      <c r="E115" s="11" t="inlineStr"/>
+      <c r="F115" s="11" t="inlineStr">
+        <is>
+          <t>LITTERALIS</t>
+        </is>
+      </c>
+      <c r="G115" s="11" t="inlineStr">
+        <is>
+          <t>Commande sans prestation</t>
+        </is>
+      </c>
+      <c r="H115" s="11" t="inlineStr"/>
+      <c r="I115" s="11" t="inlineStr">
+        <is>
+          <t>29/07/2026</t>
+        </is>
+      </c>
+      <c r="J115" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="K115" s="11" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="L115" s="11" t="inlineStr"/>
+      <c r="M115" s="11" t="inlineStr"/>
+      <c r="N115" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O115" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="P115" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="17" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B115" s="17" t="inlineStr"/>
-      <c r="C115" s="17" t="inlineStr"/>
-      <c r="D115" s="17" t="inlineStr"/>
-      <c r="E115" s="17" t="inlineStr"/>
-      <c r="F115" s="17" t="inlineStr"/>
-      <c r="G115" s="17" t="inlineStr"/>
-      <c r="H115" s="17" t="inlineStr"/>
-      <c r="I115" s="17" t="inlineStr"/>
-      <c r="J115" s="17" t="inlineStr"/>
-      <c r="K115" s="17" t="inlineStr"/>
-      <c r="L115" s="17" t="inlineStr"/>
-      <c r="M115" s="17" t="inlineStr"/>
-      <c r="N115" s="18" t="n">
+      <c r="B116" s="17" t="inlineStr"/>
+      <c r="C116" s="17" t="inlineStr"/>
+      <c r="D116" s="17" t="inlineStr"/>
+      <c r="E116" s="17" t="inlineStr"/>
+      <c r="F116" s="17" t="inlineStr"/>
+      <c r="G116" s="17" t="inlineStr"/>
+      <c r="H116" s="17" t="inlineStr"/>
+      <c r="I116" s="17" t="inlineStr"/>
+      <c r="J116" s="17" t="inlineStr"/>
+      <c r="K116" s="17" t="inlineStr"/>
+      <c r="L116" s="17" t="inlineStr"/>
+      <c r="M116" s="17" t="inlineStr"/>
+      <c r="N116" s="18" t="n">
         <v>67747.69399999999</v>
       </c>
-      <c r="O115" s="18" t="n">
+      <c r="O116" s="18" t="n">
         <v>1053.15</v>
       </c>
-      <c r="P115" s="18" t="n">
-        <v>10.1</v>
+      <c r="P116" s="18" t="n">
+        <v>9.890000000000001</v>
       </c>
     </row>
   </sheetData>
@@ -8934,6 +8986,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A112" r:id="rId108"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A113" r:id="rId109"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A114" r:id="rId110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A115" r:id="rId111"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -9508,16 +9561,16 @@
         </is>
       </c>
       <c r="B5" s="14" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C5" s="14" t="n">
-        <v>17.25</v>
+        <v>18</v>
       </c>
       <c r="D5" s="14" t="n">
-        <v>2.75</v>
+        <v>3.25</v>
       </c>
       <c r="E5" s="14" t="n">
-        <v>100</v>
+        <v>102.25</v>
       </c>
       <c r="F5" s="14" t="n">
         <v>22</v>
@@ -9527,7 +9580,7 @@
       </c>
       <c r="H5" s="21" t="inlineStr">
         <is>
-          <t>16.6%</t>
+          <t>17.0%</t>
         </is>
       </c>
     </row>

--- a/jira_export_2026-08-14.xlsx
+++ b/jira_export_2026-08-14.xlsx
@@ -815,7 +815,7 @@
     <row r="16" ht="26" customHeight="1">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>176 h</t>
+          <t>215 h</t>
         </is>
       </c>
       <c r="B16" s="7" t="n"/>
@@ -829,7 +829,7 @@
       <c r="F16" s="7" t="n"/>
       <c r="G16" s="8" t="inlineStr">
         <is>
-          <t>45.4%</t>
+          <t>55.5%</t>
         </is>
       </c>
       <c r="H16" s="7" t="n"/>
@@ -933,7 +933,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P116"/>
+  <dimension ref="A1:P117"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="43" customWidth="1" min="1" max="1"/>
@@ -3029,7 +3029,7 @@
         <v>2</v>
       </c>
       <c r="K32" s="14" t="n">
-        <v>8.25</v>
+        <v>8.75</v>
       </c>
       <c r="L32" s="14" t="inlineStr">
         <is>
@@ -3048,7 +3048,7 @@
         <v>416.29</v>
       </c>
       <c r="P32" s="15" t="n">
-        <v>50.46</v>
+        <v>47.58</v>
       </c>
     </row>
     <row r="33">
@@ -3893,7 +3893,7 @@
         <v>3</v>
       </c>
       <c r="K44" s="14" t="n">
-        <v>2.25</v>
+        <v>3.38</v>
       </c>
       <c r="L44" s="14" t="inlineStr">
         <is>
@@ -3965,7 +3965,7 @@
         <v>3</v>
       </c>
       <c r="K45" s="11" t="n">
-        <v>2.25</v>
+        <v>3.38</v>
       </c>
       <c r="L45" s="11" t="inlineStr">
         <is>
@@ -4469,7 +4469,7 @@
         <v>4</v>
       </c>
       <c r="K52" s="14" t="n">
-        <v>1.5</v>
+        <v>4</v>
       </c>
       <c r="L52" s="14" t="inlineStr"/>
       <c r="M52" s="14" t="inlineStr"/>
@@ -5745,7 +5745,7 @@
         <v>6</v>
       </c>
       <c r="K70" s="14" t="n">
-        <v>0.5</v>
+        <v>4</v>
       </c>
       <c r="L70" s="14" t="inlineStr">
         <is>
@@ -6249,7 +6249,7 @@
         <v>7</v>
       </c>
       <c r="K77" s="11" t="n">
-        <v>0.08</v>
+        <v>2.25</v>
       </c>
       <c r="L77" s="11" t="inlineStr">
         <is>
@@ -6321,7 +6321,7 @@
         <v>7</v>
       </c>
       <c r="K78" s="14" t="n">
-        <v>0.08</v>
+        <v>2.25</v>
       </c>
       <c r="L78" s="14" t="inlineStr">
         <is>
@@ -6393,7 +6393,7 @@
         <v>7</v>
       </c>
       <c r="K79" s="11" t="n">
-        <v>0.08</v>
+        <v>2.25</v>
       </c>
       <c r="L79" s="11" t="inlineStr">
         <is>
@@ -6965,7 +6965,7 @@
         <v>9</v>
       </c>
       <c r="K87" s="11" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L87" s="11" t="inlineStr">
         <is>
@@ -7336,12 +7336,12 @@
     <row r="93">
       <c r="A93" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-22757</t>
+          <t>PDMDEP-23918</t>
         </is>
       </c>
       <c r="B93" s="11" t="inlineStr">
         <is>
-          <t>BREST METROPOLE - DEPLOIEMENT DE LITTERALIS EXPERT</t>
+          <t>[CD94 - VAL DE MARNE] - Déploiement Littéralis Expert</t>
         </is>
       </c>
       <c r="C93" s="11" t="inlineStr">
@@ -7351,7 +7351,7 @@
       </c>
       <c r="D93" s="11" t="inlineStr">
         <is>
-          <t>BREST METROPOLE</t>
+          <t>DEPARTEMENT DU VAL DE MARNE (CD 94)</t>
         </is>
       </c>
       <c r="E93" s="11" t="n">
@@ -7374,23 +7374,23 @@
       </c>
       <c r="I93" s="11" t="inlineStr">
         <is>
-          <t>01/07/2025</t>
+          <t>26/08/2025</t>
         </is>
       </c>
       <c r="J93" s="11" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="K93" s="11" t="n">
-        <v>1.19</v>
+        <v>0.5</v>
       </c>
       <c r="L93" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-30081</t>
+          <t>PDMDEP-28055</t>
         </is>
       </c>
       <c r="M93" s="11" t="inlineStr">
         <is>
-          <t>00152628</t>
+          <t>499132</t>
         </is>
       </c>
       <c r="N93" s="12" t="n">
@@ -7455,12 +7455,12 @@
       </c>
       <c r="L94" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-30080</t>
+          <t>PDMDEP-30081</t>
         </is>
       </c>
       <c r="M94" s="14" t="inlineStr">
         <is>
-          <t>00152635</t>
+          <t>00152628</t>
         </is>
       </c>
       <c r="N94" s="15" t="n">
@@ -7491,7 +7491,7 @@
       </c>
       <c r="D95" s="11" t="inlineStr">
         <is>
-          <t>Brest Métropole</t>
+          <t>BREST METROPOLE</t>
         </is>
       </c>
       <c r="E95" s="11" t="n">
@@ -7525,12 +7525,12 @@
       </c>
       <c r="L95" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-30079</t>
+          <t>PDMDEP-30080</t>
         </is>
       </c>
       <c r="M95" s="11" t="inlineStr">
         <is>
-          <t>00152632</t>
+          <t>00152635</t>
         </is>
       </c>
       <c r="N95" s="12" t="n">
@@ -7561,7 +7561,7 @@
       </c>
       <c r="D96" s="14" t="inlineStr">
         <is>
-          <t>BREST METROPOLE</t>
+          <t>Brest Métropole</t>
         </is>
       </c>
       <c r="E96" s="14" t="n">
@@ -7595,12 +7595,12 @@
       </c>
       <c r="L96" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-27365</t>
+          <t>PDMDEP-30079</t>
         </is>
       </c>
       <c r="M96" s="14" t="inlineStr">
         <is>
-          <t>491593</t>
+          <t>00152632</t>
         </is>
       </c>
       <c r="N96" s="15" t="n">
@@ -7616,22 +7616,22 @@
     <row r="97">
       <c r="A97" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-21661</t>
+          <t>PDMDEP-22757</t>
         </is>
       </c>
       <c r="B97" s="11" t="inlineStr">
         <is>
-          <t>[Grand Dax] - Pastell</t>
+          <t>BREST METROPOLE - DEPLOIEMENT DE LITTERALIS EXPERT</t>
         </is>
       </c>
       <c r="C97" s="11" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D97" s="11" t="inlineStr">
         <is>
-          <t>GRAND DAX</t>
+          <t>BREST METROPOLE</t>
         </is>
       </c>
       <c r="E97" s="11" t="n">
@@ -7649,34 +7649,34 @@
       </c>
       <c r="H97" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I97" s="11" t="inlineStr">
         <is>
-          <t>07/05/2025</t>
+          <t>01/07/2025</t>
         </is>
       </c>
       <c r="J97" s="11" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="K97" s="11" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="L97" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-27373</t>
+          <t>PDMDEP-27365</t>
         </is>
       </c>
       <c r="M97" s="11" t="inlineStr">
         <is>
-          <t>466234</t>
+          <t>491593</t>
         </is>
       </c>
       <c r="N97" s="12" t="n">
-        <v>401</v>
-      </c>
-      <c r="O97" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O97" s="12" t="n">
         <v>0</v>
       </c>
       <c r="P97" s="12" t="n">
@@ -7686,22 +7686,22 @@
     <row r="98">
       <c r="A98" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-21249</t>
+          <t>PDMDEP-21661</t>
         </is>
       </c>
       <c r="B98" s="14" t="inlineStr">
         <is>
-          <t>[MONTPELLIER MMM] - Interface Pastell</t>
+          <t>[Grand Dax] - Pastell</t>
         </is>
       </c>
       <c r="C98" s="14" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D98" s="14" t="inlineStr">
         <is>
-          <t>[MONTPELLIER MMM] - Interface Pastell</t>
+          <t>GRAND DAX</t>
         </is>
       </c>
       <c r="E98" s="14" t="n">
@@ -7717,24 +7717,36 @@
           <t>Projet</t>
         </is>
       </c>
-      <c r="H98" s="14" t="inlineStr"/>
+      <c r="H98" s="14" t="inlineStr">
+        <is>
+          <t>Vente additionnelle</t>
+        </is>
+      </c>
       <c r="I98" s="14" t="inlineStr">
         <is>
-          <t>23/04/2025</t>
+          <t>07/05/2025</t>
         </is>
       </c>
       <c r="J98" s="14" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="K98" s="14" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="L98" s="14" t="inlineStr"/>
-      <c r="M98" s="14" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="L98" s="14" t="inlineStr">
+        <is>
+          <t>PDMDEP-27373</t>
+        </is>
+      </c>
+      <c r="M98" s="14" t="inlineStr">
+        <is>
+          <t>466234</t>
+        </is>
+      </c>
       <c r="N98" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O98" s="15" t="n">
+        <v>401</v>
+      </c>
+      <c r="O98" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P98" s="15" t="n">
@@ -7744,22 +7756,22 @@
     <row r="99">
       <c r="A99" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-21222</t>
+          <t>PDMDEP-21249</t>
         </is>
       </c>
       <c r="B99" s="11" t="inlineStr">
         <is>
-          <t>[Issy les Moulineaux] Litteralis Expert</t>
+          <t>[MONTPELLIER MMM] - Interface Pastell</t>
         </is>
       </c>
       <c r="C99" s="11" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D99" s="11" t="inlineStr">
         <is>
-          <t>ISSY LES MOULINEAUX</t>
+          <t>[MONTPELLIER MMM] - Interface Pastell</t>
         </is>
       </c>
       <c r="E99" s="11" t="n">
@@ -7775,11 +7787,7 @@
           <t>Projet</t>
         </is>
       </c>
-      <c r="H99" s="11" t="inlineStr">
-        <is>
-          <t>Nouveau déploiement</t>
-        </is>
-      </c>
+      <c r="H99" s="11" t="inlineStr"/>
       <c r="I99" s="11" t="inlineStr">
         <is>
           <t>23/04/2025</t>
@@ -7789,18 +7797,10 @@
         <v>16</v>
       </c>
       <c r="K99" s="11" t="n">
-        <v>5.75</v>
-      </c>
-      <c r="L99" s="11" t="inlineStr">
-        <is>
-          <t>PDMDEP-28036</t>
-        </is>
-      </c>
-      <c r="M99" s="11" t="inlineStr">
-        <is>
-          <t>483799</t>
-        </is>
-      </c>
+        <v>0.5</v>
+      </c>
+      <c r="L99" s="11" t="inlineStr"/>
+      <c r="M99" s="11" t="inlineStr"/>
       <c r="N99" s="12" t="n">
         <v>0</v>
       </c>
@@ -7814,12 +7814,12 @@
     <row r="100">
       <c r="A100" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-20907</t>
+          <t>PDMDEP-21222</t>
         </is>
       </c>
       <c r="B100" s="14" t="inlineStr">
         <is>
-          <t>[Saint-Pierre (Réunion)] Accompagnement modélisation AME Littéralis Expert</t>
+          <t>[Issy les Moulineaux] Litteralis Expert</t>
         </is>
       </c>
       <c r="C100" s="14" t="inlineStr">
@@ -7829,7 +7829,7 @@
       </c>
       <c r="D100" s="14" t="inlineStr">
         <is>
-          <t>SAINT PIERRE (LA REUNION)</t>
+          <t>ISSY LES MOULINEAUX</t>
         </is>
       </c>
       <c r="E100" s="14" t="n">
@@ -7847,34 +7847,34 @@
       </c>
       <c r="H100" s="14" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I100" s="14" t="inlineStr">
         <is>
-          <t>14/04/2025</t>
+          <t>23/04/2025</t>
         </is>
       </c>
       <c r="J100" s="14" t="n">
         <v>16</v>
       </c>
       <c r="K100" s="14" t="n">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="L100" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-28034</t>
+          <t>PDMDEP-28036</t>
         </is>
       </c>
       <c r="M100" s="14" t="inlineStr">
         <is>
-          <t>475575</t>
+          <t>483799</t>
         </is>
       </c>
       <c r="N100" s="15" t="n">
-        <v>230</v>
-      </c>
-      <c r="O100" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O100" s="15" t="n">
         <v>0</v>
       </c>
       <c r="P100" s="15" t="n">
@@ -7884,22 +7884,22 @@
     <row r="101">
       <c r="A101" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-20187</t>
+          <t>PDMDEP-20907</t>
         </is>
       </c>
       <c r="B101" s="11" t="inlineStr">
         <is>
-          <t>[ANTIBES] - Interface AIRS Delib</t>
+          <t>[Saint-Pierre (Réunion)] Accompagnement modélisation AME Littéralis Expert</t>
         </is>
       </c>
       <c r="C101" s="11" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D101" s="11" t="inlineStr">
         <is>
-          <t>Antibes</t>
+          <t>SAINT PIERRE (LA REUNION)</t>
         </is>
       </c>
       <c r="E101" s="11" t="n">
@@ -7912,27 +7912,39 @@
       </c>
       <c r="G101" s="11" t="inlineStr">
         <is>
-          <t>Rework</t>
-        </is>
-      </c>
-      <c r="H101" s="11" t="inlineStr"/>
+          <t>Projet</t>
+        </is>
+      </c>
+      <c r="H101" s="11" t="inlineStr">
+        <is>
+          <t>Vente additionnelle</t>
+        </is>
+      </c>
       <c r="I101" s="11" t="inlineStr">
         <is>
-          <t>19/03/2025</t>
+          <t>14/04/2025</t>
         </is>
       </c>
       <c r="J101" s="11" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="K101" s="11" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="L101" s="11" t="inlineStr"/>
-      <c r="M101" s="11" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="L101" s="11" t="inlineStr">
+        <is>
+          <t>PDMDEP-28034</t>
+        </is>
+      </c>
+      <c r="M101" s="11" t="inlineStr">
+        <is>
+          <t>475575</t>
+        </is>
+      </c>
       <c r="N101" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O101" s="12" t="n">
+        <v>230</v>
+      </c>
+      <c r="O101" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P101" s="12" t="n">
@@ -7942,22 +7954,22 @@
     <row r="102">
       <c r="A102" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-20032</t>
+          <t>PDMDEP-20187</t>
         </is>
       </c>
       <c r="B102" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">[SENS] Littéralis Expert </t>
+          <t>[ANTIBES] - Interface AIRS Delib</t>
         </is>
       </c>
       <c r="C102" s="14" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D102" s="14" t="inlineStr">
         <is>
-          <t>SENS</t>
+          <t>Antibes</t>
         </is>
       </c>
       <c r="E102" s="14" t="n">
@@ -7970,35 +7982,23 @@
       </c>
       <c r="G102" s="14" t="inlineStr">
         <is>
-          <t>Projet</t>
-        </is>
-      </c>
-      <c r="H102" s="14" t="inlineStr">
-        <is>
-          <t>Nouveau déploiement</t>
-        </is>
-      </c>
+          <t>Rework</t>
+        </is>
+      </c>
+      <c r="H102" s="14" t="inlineStr"/>
       <c r="I102" s="14" t="inlineStr">
         <is>
-          <t>14/03/2025</t>
+          <t>19/03/2025</t>
         </is>
       </c>
       <c r="J102" s="14" t="n">
         <v>17</v>
       </c>
       <c r="K102" s="14" t="n">
-        <v>2</v>
-      </c>
-      <c r="L102" s="14" t="inlineStr">
-        <is>
-          <t>PDMDEP-28027</t>
-        </is>
-      </c>
-      <c r="M102" s="14" t="inlineStr">
-        <is>
-          <t>470688</t>
-        </is>
-      </c>
+        <v>1.25</v>
+      </c>
+      <c r="L102" s="14" t="inlineStr"/>
+      <c r="M102" s="14" t="inlineStr"/>
       <c r="N102" s="15" t="n">
         <v>0</v>
       </c>
@@ -8012,12 +8012,12 @@
     <row r="103">
       <c r="A103" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-18240</t>
+          <t>PDMDEP-20032</t>
         </is>
       </c>
       <c r="B103" s="11" t="inlineStr">
         <is>
-          <t>[BIARRITZ] - Projet Littéralis Expert (Cmde1 - Mise en service - abo)</t>
+          <t xml:space="preserve">[SENS] Littéralis Expert </t>
         </is>
       </c>
       <c r="C103" s="11" t="inlineStr">
@@ -8027,7 +8027,7 @@
       </c>
       <c r="D103" s="11" t="inlineStr">
         <is>
-          <t>Biarritz</t>
+          <t>SENS</t>
         </is>
       </c>
       <c r="E103" s="11" t="n">
@@ -8040,7 +8040,7 @@
       </c>
       <c r="G103" s="11" t="inlineStr">
         <is>
-          <t>Rework</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H103" s="11" t="inlineStr">
@@ -8050,17 +8050,25 @@
       </c>
       <c r="I103" s="11" t="inlineStr">
         <is>
-          <t>20/12/2024</t>
+          <t>14/03/2025</t>
         </is>
       </c>
       <c r="J103" s="11" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="K103" s="11" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="L103" s="11" t="inlineStr"/>
-      <c r="M103" s="11" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="L103" s="11" t="inlineStr">
+        <is>
+          <t>PDMDEP-28027</t>
+        </is>
+      </c>
+      <c r="M103" s="11" t="inlineStr">
+        <is>
+          <t>470688</t>
+        </is>
+      </c>
       <c r="N103" s="12" t="n">
         <v>0</v>
       </c>
@@ -8074,12 +8082,12 @@
     <row r="104">
       <c r="A104" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-18196</t>
+          <t>PDMDEP-18240</t>
         </is>
       </c>
       <c r="B104" s="14" t="inlineStr">
         <is>
-          <t>[GENTILLY] - Litteralis Expert SAAS</t>
+          <t>[BIARRITZ] - Projet Littéralis Expert (Cmde1 - Mise en service - abo)</t>
         </is>
       </c>
       <c r="C104" s="14" t="inlineStr">
@@ -8089,7 +8097,7 @@
       </c>
       <c r="D104" s="14" t="inlineStr">
         <is>
-          <t>Gentilly</t>
+          <t>Biarritz</t>
         </is>
       </c>
       <c r="E104" s="14" t="n">
@@ -8112,14 +8120,14 @@
       </c>
       <c r="I104" s="14" t="inlineStr">
         <is>
-          <t>19/12/2024</t>
+          <t>20/12/2024</t>
         </is>
       </c>
       <c r="J104" s="14" t="n">
         <v>20</v>
       </c>
       <c r="K104" s="14" t="n">
-        <v>1.5</v>
+        <v>5.75</v>
       </c>
       <c r="L104" s="14" t="inlineStr"/>
       <c r="M104" s="14" t="inlineStr"/>
@@ -8136,22 +8144,22 @@
     <row r="105">
       <c r="A105" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-18115</t>
+          <t>PDMDEP-18196</t>
         </is>
       </c>
       <c r="B105" s="11" t="inlineStr">
         <is>
-          <t>[Bischwiller] Migration + Pax + M2M</t>
+          <t>[GENTILLY] - Litteralis Expert SAAS</t>
         </is>
       </c>
       <c r="C105" s="11" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D105" s="11" t="inlineStr">
         <is>
-          <t>BISCHWILLER</t>
+          <t>Gentilly</t>
         </is>
       </c>
       <c r="E105" s="11" t="n">
@@ -8159,44 +8167,36 @@
       </c>
       <c r="F105" s="11" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G105" s="11" t="inlineStr">
         <is>
-          <t>Projet</t>
+          <t>Rework</t>
         </is>
       </c>
       <c r="H105" s="11" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I105" s="11" t="inlineStr">
         <is>
-          <t>17/12/2024</t>
+          <t>19/12/2024</t>
         </is>
       </c>
       <c r="J105" s="11" t="n">
         <v>20</v>
       </c>
       <c r="K105" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L105" s="11" t="inlineStr">
-        <is>
-          <t>PDMDEP-28019</t>
-        </is>
-      </c>
-      <c r="M105" s="11" t="inlineStr">
-        <is>
-          <t>455151</t>
-        </is>
-      </c>
+        <v>1.5</v>
+      </c>
+      <c r="L105" s="11" t="inlineStr"/>
+      <c r="M105" s="11" t="inlineStr"/>
       <c r="N105" s="12" t="n">
-        <v>240</v>
-      </c>
-      <c r="O105" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O105" s="12" t="n">
         <v>0</v>
       </c>
       <c r="P105" s="12" t="n">
@@ -8206,22 +8206,22 @@
     <row r="106">
       <c r="A106" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-18037</t>
+          <t>PDMDEP-18115</t>
         </is>
       </c>
       <c r="B106" s="14" t="inlineStr">
         <is>
-          <t>[LE PERREUX SUR MARNE] Modélisation/Paramétrage 2J civil net finances</t>
+          <t>[Bischwiller] Migration + Pax + M2M</t>
         </is>
       </c>
       <c r="C106" s="14" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D106" s="14" t="inlineStr">
         <is>
-          <t>LE PERREUX SUR MARNE</t>
+          <t>BISCHWILLER</t>
         </is>
       </c>
       <c r="E106" s="14" t="n">
@@ -8229,7 +8229,7 @@
       </c>
       <c r="F106" s="14" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G106" s="14" t="inlineStr">
@@ -8239,12 +8239,12 @@
       </c>
       <c r="H106" s="14" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I106" s="14" t="inlineStr">
         <is>
-          <t>12/12/2024</t>
+          <t>17/12/2024</t>
         </is>
       </c>
       <c r="J106" s="14" t="n">
@@ -8255,16 +8255,16 @@
       </c>
       <c r="L106" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-28023</t>
+          <t>PDMDEP-28019</t>
         </is>
       </c>
       <c r="M106" s="14" t="inlineStr">
         <is>
-          <t>454387</t>
+          <t>455151</t>
         </is>
       </c>
       <c r="N106" s="15" t="n">
-        <v>557.145</v>
+        <v>240</v>
       </c>
       <c r="O106" s="16" t="n">
         <v>0</v>
@@ -8276,22 +8276,22 @@
     <row r="107">
       <c r="A107" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-15695</t>
+          <t>PDMDEP-18037</t>
         </is>
       </c>
       <c r="B107" s="11" t="inlineStr">
         <is>
-          <t>[CD50 - MANCHE] Interface Pastell</t>
+          <t>[LE PERREUX SUR MARNE] Modélisation/Paramétrage 2J civil net finances</t>
         </is>
       </c>
       <c r="C107" s="11" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D107" s="11" t="inlineStr">
         <is>
-          <t>CD Manche</t>
+          <t>LE PERREUX SUR MARNE</t>
         </is>
       </c>
       <c r="E107" s="11" t="n">
@@ -8304,7 +8304,7 @@
       </c>
       <c r="G107" s="11" t="inlineStr">
         <is>
-          <t>Rework</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H107" s="11" t="inlineStr">
@@ -8314,21 +8314,29 @@
       </c>
       <c r="I107" s="11" t="inlineStr">
         <is>
-          <t>17/06/2024</t>
+          <t>12/12/2024</t>
         </is>
       </c>
       <c r="J107" s="11" t="n">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="K107" s="11" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="L107" s="11" t="inlineStr"/>
-      <c r="M107" s="11" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="L107" s="11" t="inlineStr">
+        <is>
+          <t>PDMDEP-28023</t>
+        </is>
+      </c>
+      <c r="M107" s="11" t="inlineStr">
+        <is>
+          <t>454387</t>
+        </is>
+      </c>
       <c r="N107" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O107" s="12" t="n">
+        <v>557.145</v>
+      </c>
+      <c r="O107" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P107" s="12" t="n">
@@ -8338,22 +8346,22 @@
     <row r="108">
       <c r="A108" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-14798</t>
+          <t>PDMDEP-15695</t>
         </is>
       </c>
       <c r="B108" s="14" t="inlineStr">
         <is>
-          <t>[CD 92 Hauts-de-Seine] Crédit 5j de param</t>
+          <t>[CD50 - MANCHE] Interface Pastell</t>
         </is>
       </c>
       <c r="C108" s="14" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D108" s="14" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DES HAUTS DE SEINE (CD 92)</t>
+          <t>CD Manche</t>
         </is>
       </c>
       <c r="E108" s="14" t="n">
@@ -8376,25 +8384,17 @@
       </c>
       <c r="I108" s="14" t="inlineStr">
         <is>
-          <t>05/04/2024</t>
+          <t>17/06/2024</t>
         </is>
       </c>
       <c r="J108" s="14" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="K108" s="14" t="n">
         <v>2.5</v>
       </c>
-      <c r="L108" s="14" t="inlineStr">
-        <is>
-          <t>PDMDEP-28003</t>
-        </is>
-      </c>
-      <c r="M108" s="14" t="inlineStr">
-        <is>
-          <t>412981</t>
-        </is>
-      </c>
+      <c r="L108" s="14" t="inlineStr"/>
+      <c r="M108" s="14" t="inlineStr"/>
       <c r="N108" s="15" t="n">
         <v>0</v>
       </c>
@@ -8408,22 +8408,22 @@
     <row r="109">
       <c r="A109" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-14118</t>
+          <t>PDMDEP-14798</t>
         </is>
       </c>
       <c r="B109" s="11" t="inlineStr">
         <is>
-          <t>[SURESNES] Interface FAST-Parapheur</t>
+          <t>[CD 92 Hauts-de-Seine] Crédit 5j de param</t>
         </is>
       </c>
       <c r="C109" s="11" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D109" s="11" t="inlineStr">
         <is>
-          <t>Suresnes</t>
+          <t>CONSEIL DEPARTEMENTAL DES HAUTS DE SEINE (CD 92)</t>
         </is>
       </c>
       <c r="E109" s="11" t="n">
@@ -8446,17 +8446,25 @@
       </c>
       <c r="I109" s="11" t="inlineStr">
         <is>
-          <t>01/02/2024</t>
+          <t>05/04/2024</t>
         </is>
       </c>
       <c r="J109" s="11" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="K109" s="11" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="L109" s="11" t="inlineStr"/>
-      <c r="M109" s="11" t="inlineStr"/>
+        <v>2.5</v>
+      </c>
+      <c r="L109" s="11" t="inlineStr">
+        <is>
+          <t>PDMDEP-28003</t>
+        </is>
+      </c>
+      <c r="M109" s="11" t="inlineStr">
+        <is>
+          <t>412981</t>
+        </is>
+      </c>
       <c r="N109" s="12" t="n">
         <v>0</v>
       </c>
@@ -8470,22 +8478,22 @@
     <row r="110">
       <c r="A110" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-12747</t>
+          <t>PDMDEP-14118</t>
         </is>
       </c>
       <c r="B110" s="14" t="inlineStr">
         <is>
-          <t>[FOUGERES] ARPEGE</t>
+          <t>[SURESNES] Interface FAST-Parapheur</t>
         </is>
       </c>
       <c r="C110" s="14" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D110" s="14" t="inlineStr">
         <is>
-          <t>FOUGERES</t>
+          <t>Suresnes</t>
         </is>
       </c>
       <c r="E110" s="14" t="n">
@@ -8498,7 +8506,7 @@
       </c>
       <c r="G110" s="14" t="inlineStr">
         <is>
-          <t>Projet</t>
+          <t>Rework</t>
         </is>
       </c>
       <c r="H110" s="14" t="inlineStr">
@@ -8508,25 +8516,17 @@
       </c>
       <c r="I110" s="14" t="inlineStr">
         <is>
-          <t>26/09/2023</t>
+          <t>01/02/2024</t>
         </is>
       </c>
       <c r="J110" s="14" t="n">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="K110" s="14" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="L110" s="14" t="inlineStr">
-        <is>
-          <t>PDMDEP-27990</t>
-        </is>
-      </c>
-      <c r="M110" s="14" t="inlineStr">
-        <is>
-          <t>406296</t>
-        </is>
-      </c>
+        <v>0.5</v>
+      </c>
+      <c r="L110" s="14" t="inlineStr"/>
+      <c r="M110" s="14" t="inlineStr"/>
       <c r="N110" s="15" t="n">
         <v>0</v>
       </c>
@@ -8540,22 +8540,22 @@
     <row r="111">
       <c r="A111" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-12666</t>
+          <t>PDMDEP-12747</t>
         </is>
       </c>
       <c r="B111" s="11" t="inlineStr">
         <is>
-          <t>[LE MANS METROPOLE] Littéralis Expert</t>
+          <t>[FOUGERES] ARPEGE</t>
         </is>
       </c>
       <c r="C111" s="11" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D111" s="11" t="inlineStr">
         <is>
-          <t>LE MANS METROPOLE</t>
+          <t>FOUGERES</t>
         </is>
       </c>
       <c r="E111" s="11" t="n">
@@ -8568,17 +8568,17 @@
       </c>
       <c r="G111" s="11" t="inlineStr">
         <is>
-          <t>Rework</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H111" s="11" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I111" s="11" t="inlineStr">
         <is>
-          <t>19/09/2023</t>
+          <t>26/09/2023</t>
         </is>
       </c>
       <c r="J111" s="11" t="n">
@@ -8589,12 +8589,12 @@
       </c>
       <c r="L111" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-34532</t>
+          <t>PDMDEP-27990</t>
         </is>
       </c>
       <c r="M111" s="11" t="inlineStr">
         <is>
-          <t>412263</t>
+          <t>406296</t>
         </is>
       </c>
       <c r="N111" s="12" t="n">
@@ -8610,12 +8610,12 @@
     <row r="112">
       <c r="A112" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-12443</t>
+          <t>PDMDEP-12666</t>
         </is>
       </c>
       <c r="B112" s="14" t="inlineStr">
         <is>
-          <t>[CD79 - LES DEUX SEVRES] LITTERALIS EXPERT</t>
+          <t>[LE MANS METROPOLE] Littéralis Expert</t>
         </is>
       </c>
       <c r="C112" s="14" t="inlineStr">
@@ -8625,7 +8625,7 @@
       </c>
       <c r="D112" s="14" t="inlineStr">
         <is>
-          <t>CD79 - Deux Sèvres</t>
+          <t>LE MANS METROPOLE</t>
         </is>
       </c>
       <c r="E112" s="14" t="n">
@@ -8648,17 +8648,25 @@
       </c>
       <c r="I112" s="14" t="inlineStr">
         <is>
-          <t>04/09/2023</t>
+          <t>19/09/2023</t>
         </is>
       </c>
       <c r="J112" s="14" t="n">
         <v>35</v>
       </c>
       <c r="K112" s="14" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="L112" s="14" t="inlineStr"/>
-      <c r="M112" s="14" t="inlineStr"/>
+        <v>1.5</v>
+      </c>
+      <c r="L112" s="14" t="inlineStr">
+        <is>
+          <t>PDMDEP-34532</t>
+        </is>
+      </c>
+      <c r="M112" s="14" t="inlineStr">
+        <is>
+          <t>412263</t>
+        </is>
+      </c>
       <c r="N112" s="15" t="n">
         <v>0</v>
       </c>
@@ -8672,28 +8680,26 @@
     <row r="113">
       <c r="A113" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-12222</t>
+          <t>PDMDEP-12443</t>
         </is>
       </c>
       <c r="B113" s="11" t="inlineStr">
         <is>
-          <t>[CD 14] Paramétrages</t>
+          <t>[CD79 - LES DEUX SEVRES] LITTERALIS EXPERT</t>
         </is>
       </c>
       <c r="C113" s="11" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D113" s="11" t="inlineStr">
         <is>
-          <t>CD14</t>
-        </is>
-      </c>
-      <c r="E113" s="11" t="inlineStr">
-        <is>
-          <t>Modélisation spécifique</t>
-        </is>
+          <t>CD79 - Deux Sèvres</t>
+        </is>
+      </c>
+      <c r="E113" s="11" t="n">
+        <v/>
       </c>
       <c r="F113" s="11" t="inlineStr">
         <is>
@@ -8707,7 +8713,7 @@
       </c>
       <c r="H113" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I113" s="11" t="inlineStr">
@@ -8719,7 +8725,7 @@
         <v>35</v>
       </c>
       <c r="K113" s="11" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="L113" s="11" t="inlineStr"/>
       <c r="M113" s="11" t="inlineStr"/>
@@ -8736,23 +8742,27 @@
     <row r="114">
       <c r="A114" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-11477</t>
+          <t>PDMDEP-12222</t>
         </is>
       </c>
       <c r="B114" s="14" t="inlineStr">
         <is>
-          <t>[MONTPELLIER MMM - Module AC] LITTERALIS EXPERT</t>
-        </is>
-      </c>
-      <c r="C114" s="14" t="inlineStr"/>
+          <t>[CD 14] Paramétrages</t>
+        </is>
+      </c>
+      <c r="C114" s="14" t="inlineStr">
+        <is>
+          <t>Fabien REUTENAUER</t>
+        </is>
+      </c>
       <c r="D114" s="14" t="inlineStr">
         <is>
-          <t>MONTPELLIER MMM</t>
+          <t>CD14</t>
         </is>
       </c>
       <c r="E114" s="14" t="inlineStr">
         <is>
-          <t>Déploiement Module AC</t>
+          <t>Modélisation spécifique</t>
         </is>
       </c>
       <c r="F114" s="14" t="inlineStr">
@@ -8767,19 +8777,19 @@
       </c>
       <c r="H114" s="14" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I114" s="14" t="inlineStr">
         <is>
-          <t>03/09/2023</t>
+          <t>04/09/2023</t>
         </is>
       </c>
       <c r="J114" s="14" t="n">
         <v>35</v>
       </c>
       <c r="K114" s="14" t="n">
-        <v>4.5</v>
+        <v>1</v>
       </c>
       <c r="L114" s="14" t="inlineStr"/>
       <c r="M114" s="14" t="inlineStr"/>
@@ -8796,21 +8806,25 @@
     <row r="115">
       <c r="A115" s="10" t="inlineStr">
         <is>
-          <t>PSC-1326</t>
+          <t>PDMDEP-11477</t>
         </is>
       </c>
       <c r="B115" s="11" t="inlineStr">
         <is>
-          <t>MAIRIE DE SAINT-ISMIER</t>
+          <t>[MONTPELLIER MMM - Module AC] LITTERALIS EXPERT</t>
         </is>
       </c>
       <c r="C115" s="11" t="inlineStr"/>
       <c r="D115" s="11" t="inlineStr">
         <is>
-          <t>MAIRIE DE SAINT-ISMIER</t>
-        </is>
-      </c>
-      <c r="E115" s="11" t="inlineStr"/>
+          <t>MONTPELLIER MMM</t>
+        </is>
+      </c>
+      <c r="E115" s="11" t="inlineStr">
+        <is>
+          <t>Déploiement Module AC</t>
+        </is>
+      </c>
       <c r="F115" s="11" t="inlineStr">
         <is>
           <t>LITTERALIS</t>
@@ -8818,20 +8832,24 @@
       </c>
       <c r="G115" s="11" t="inlineStr">
         <is>
-          <t>Commande sans prestation</t>
-        </is>
-      </c>
-      <c r="H115" s="11" t="inlineStr"/>
+          <t>Rework</t>
+        </is>
+      </c>
+      <c r="H115" s="11" t="inlineStr">
+        <is>
+          <t>Nouveau déploiement</t>
+        </is>
+      </c>
       <c r="I115" s="11" t="inlineStr">
         <is>
-          <t>29/07/2026</t>
+          <t>03/09/2023</t>
         </is>
       </c>
       <c r="J115" s="11" t="n">
-        <v>1</v>
+        <v>35</v>
       </c>
       <c r="K115" s="11" t="n">
-        <v>0.5</v>
+        <v>4.5</v>
       </c>
       <c r="L115" s="11" t="inlineStr"/>
       <c r="M115" s="11" t="inlineStr"/>
@@ -8846,31 +8864,83 @@
       </c>
     </row>
     <row r="116">
-      <c r="A116" s="17" t="inlineStr">
+      <c r="A116" s="13" t="inlineStr">
+        <is>
+          <t>PSC-1326</t>
+        </is>
+      </c>
+      <c r="B116" s="14" t="inlineStr">
+        <is>
+          <t>MAIRIE DE SAINT-ISMIER</t>
+        </is>
+      </c>
+      <c r="C116" s="14" t="inlineStr"/>
+      <c r="D116" s="14" t="inlineStr">
+        <is>
+          <t>MAIRIE DE SAINT-ISMIER</t>
+        </is>
+      </c>
+      <c r="E116" s="14" t="inlineStr"/>
+      <c r="F116" s="14" t="inlineStr">
+        <is>
+          <t>LITTERALIS</t>
+        </is>
+      </c>
+      <c r="G116" s="14" t="inlineStr">
+        <is>
+          <t>Commande sans prestation</t>
+        </is>
+      </c>
+      <c r="H116" s="14" t="inlineStr"/>
+      <c r="I116" s="14" t="inlineStr">
+        <is>
+          <t>29/07/2026</t>
+        </is>
+      </c>
+      <c r="J116" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="K116" s="14" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="L116" s="14" t="inlineStr"/>
+      <c r="M116" s="14" t="inlineStr"/>
+      <c r="N116" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="O116" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="P116" s="15" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="17" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B116" s="17" t="inlineStr"/>
-      <c r="C116" s="17" t="inlineStr"/>
-      <c r="D116" s="17" t="inlineStr"/>
-      <c r="E116" s="17" t="inlineStr"/>
-      <c r="F116" s="17" t="inlineStr"/>
-      <c r="G116" s="17" t="inlineStr"/>
-      <c r="H116" s="17" t="inlineStr"/>
-      <c r="I116" s="17" t="inlineStr"/>
-      <c r="J116" s="17" t="inlineStr"/>
-      <c r="K116" s="17" t="inlineStr"/>
-      <c r="L116" s="17" t="inlineStr"/>
-      <c r="M116" s="17" t="inlineStr"/>
-      <c r="N116" s="18" t="n">
+      <c r="B117" s="17" t="inlineStr"/>
+      <c r="C117" s="17" t="inlineStr"/>
+      <c r="D117" s="17" t="inlineStr"/>
+      <c r="E117" s="17" t="inlineStr"/>
+      <c r="F117" s="17" t="inlineStr"/>
+      <c r="G117" s="17" t="inlineStr"/>
+      <c r="H117" s="17" t="inlineStr"/>
+      <c r="I117" s="17" t="inlineStr"/>
+      <c r="J117" s="17" t="inlineStr"/>
+      <c r="K117" s="17" t="inlineStr"/>
+      <c r="L117" s="17" t="inlineStr"/>
+      <c r="M117" s="17" t="inlineStr"/>
+      <c r="N117" s="18" t="n">
         <v>67747.69399999999</v>
       </c>
-      <c r="O116" s="18" t="n">
+      <c r="O117" s="18" t="n">
         <v>1053.15</v>
       </c>
-      <c r="P116" s="18" t="n">
-        <v>9.890000000000001</v>
+      <c r="P117" s="18" t="n">
+        <v>8.27</v>
       </c>
     </row>
   </sheetData>
@@ -8987,6 +9057,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A113" r:id="rId109"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A114" r:id="rId110"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A115" r:id="rId111"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A116" r:id="rId112"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -9561,26 +9632,26 @@
         </is>
       </c>
       <c r="B5" s="14" t="n">
-        <v>81</v>
+        <v>95.25</v>
       </c>
       <c r="C5" s="14" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="D5" s="14" t="n">
-        <v>3.25</v>
+        <v>5.75</v>
       </c>
       <c r="E5" s="14" t="n">
-        <v>102.25</v>
+        <v>123</v>
       </c>
       <c r="F5" s="14" t="n">
-        <v>22</v>
+        <v>35.5</v>
       </c>
       <c r="G5" s="14" t="n">
         <v>601.65</v>
       </c>
       <c r="H5" s="21" t="inlineStr">
         <is>
-          <t>17.0%</t>
+          <t>20.4%</t>
         </is>
       </c>
     </row>
@@ -9622,7 +9693,7 @@
         </is>
       </c>
       <c r="B8" s="23" t="n">
-        <v>47</v>
+        <v>51</v>
       </c>
     </row>
   </sheetData>
@@ -9710,10 +9781,10 @@
         <v>389195</v>
       </c>
       <c r="C5" s="24" t="n">
-        <v>146122</v>
+        <v>145705</v>
       </c>
       <c r="D5" s="24" t="n">
-        <v>243073</v>
+        <v>243490</v>
       </c>
       <c r="E5" s="24" t="n">
         <v>152769</v>
@@ -9722,7 +9793,7 @@
         <v>21179</v>
       </c>
       <c r="G5" s="24" t="n">
-        <v>26461</v>
+        <v>26877</v>
       </c>
     </row>
     <row r="6">
@@ -9735,10 +9806,10 @@
         <v>174711</v>
       </c>
       <c r="C6" s="25" t="n">
-        <v>70007</v>
+        <v>69591</v>
       </c>
       <c r="D6" s="25" t="n">
-        <v>104703</v>
+        <v>105120</v>
       </c>
       <c r="E6" s="25" t="n">
         <v>87288</v>
@@ -9747,7 +9818,7 @@
         <v>11307</v>
       </c>
       <c r="G6" s="25" t="n">
-        <v>3508</v>
+        <v>3924</v>
       </c>
     </row>
     <row r="7">
